--- a/storage/app/assessTemplate/annual.xlsx
+++ b/storage/app/assessTemplate/annual.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\excel\評価シートテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441DE2AF-13A8-4F09-992E-DFFB02E34B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A1D928-BB58-4E2A-8464-A74141B0A4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{FF9A62BA-2D2B-43D0-B352-DA45FE5581AE}"/>
+    <workbookView xWindow="45" yWindow="390" windowWidth="28755" windowHeight="15435" xr2:uid="{FF9A62BA-2D2B-43D0-B352-DA45FE5581AE}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（年次取得）" sheetId="2" r:id="rId1"/>
@@ -269,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="#,##0.0;[Red]\-#,##0.0"/>
     <numFmt numFmtId="177" formatCode="#,##0.00&quot;㎡&quot;"/>
     <numFmt numFmtId="178" formatCode="[$]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
@@ -278,6 +278,7 @@
     <numFmt numFmtId="181" formatCode="0.0%"/>
     <numFmt numFmtId="182" formatCode="#,##0&quot;年&quot;"/>
     <numFmt numFmtId="183" formatCode="0;_ꐀ"/>
+    <numFmt numFmtId="184" formatCode="ggge&quot;年&quot;"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1258,6 +1259,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1327,14 +1336,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1679,8 +1680,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
       <c r="N1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1690,47 +1691,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
       <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="99"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
       <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="101"/>
-      <c r="K4" s="102"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="104"/>
       <c r="L4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="99"/>
-      <c r="N4" s="103"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="105"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1779,8 +1780,8 @@
       <c r="H7" s="81"/>
       <c r="I7" s="82"/>
       <c r="J7" s="16"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="105"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="84"/>
       <c r="M7" s="17"/>
       <c r="N7" s="13"/>
     </row>
@@ -1844,11 +1845,11 @@
     </row>
     <row r="13" spans="1:15" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11"/>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="84"/>
-      <c r="E13" s="87" t="s">
+      <c r="C13" s="86"/>
+      <c r="E13" s="89" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="74" t="s">
@@ -1864,9 +1865,9 @@
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="86"/>
-      <c r="E14" s="88"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="88"/>
+      <c r="E14" s="90"/>
       <c r="G14" s="26" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1885,8 @@
     </row>
     <row r="15" spans="1:15" ht="52.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="92"/>
       <c r="D15" s="28" t="s">
         <v>17</v>
       </c>
@@ -1910,17 +1911,17 @@
     </row>
     <row r="18" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="91" t="s">
+      <c r="B18" s="93"/>
+      <c r="C18" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="87" t="s">
+      <c r="E18" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="93" t="s">
+      <c r="G18" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="94"/>
+      <c r="H18" s="96"/>
       <c r="J18" s="74" t="s">
         <v>22</v>
       </c>
@@ -1929,9 +1930,9 @@
     </row>
     <row r="19" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
-      <c r="E19" s="88"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="E19" s="90"/>
       <c r="G19" s="33"/>
       <c r="H19" s="27" t="s">
         <v>23</v>

--- a/storage/app/assessTemplate/annual.xlsx
+++ b/storage/app/assessTemplate/annual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\評価シートExcelテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\assessTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A1D928-BB58-4E2A-8464-A74141B0A4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F460F6-9DD3-4D30-8321-DCAC853E3660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="390" windowWidth="28755" windowHeight="15435" xr2:uid="{FF9A62BA-2D2B-43D0-B352-DA45FE5581AE}"/>
+    <workbookView xWindow="45" yWindow="45" windowWidth="28755" windowHeight="15435" xr2:uid="{FF9A62BA-2D2B-43D0-B352-DA45FE5581AE}"/>
   </bookViews>
   <sheets>
     <sheet name="評価表（年次取得）" sheetId="2" r:id="rId1"/>
@@ -1193,22 +1193,6 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="48" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1217,14 +1201,6 @@
     </xf>
     <xf numFmtId="182" fontId="1" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1337,6 +1313,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="7" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="21" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="48" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1680,8 +1680,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
       <c r="N1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1691,47 +1691,47 @@
       <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
       <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="101"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
       <c r="I4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="103"/>
-      <c r="K4" s="104"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="98"/>
       <c r="L4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="M4" s="101"/>
-      <c r="N4" s="105"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="99"/>
       <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -1739,8 +1739,8 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -1772,16 +1772,16 @@
     </row>
     <row r="7" spans="1:15" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="14"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="80"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="72"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
       <c r="G7" s="15"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="82"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="76"/>
       <c r="J7" s="16"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="84"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="78"/>
       <c r="M7" s="17"/>
       <c r="N7" s="13"/>
     </row>
@@ -1845,29 +1845,29 @@
     </row>
     <row r="13" spans="1:15" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A13" s="11"/>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="86"/>
-      <c r="E13" s="89" t="s">
+      <c r="C13" s="80"/>
+      <c r="E13" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="75"/>
+      <c r="H13" s="69"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="74" t="s">
+      <c r="J13" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="75"/>
+      <c r="K13" s="69"/>
       <c r="N13" s="13"/>
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
-      <c r="B14" s="87"/>
-      <c r="C14" s="88"/>
-      <c r="E14" s="90"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="E14" s="84"/>
       <c r="G14" s="26" t="s">
         <v>14</v>
       </c>
@@ -1885,8 +1885,8 @@
     </row>
     <row r="15" spans="1:15" ht="52.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="11"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="92"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="28" t="s">
         <v>17</v>
       </c>
@@ -1911,28 +1911,28 @@
     </row>
     <row r="18" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93" t="s">
+      <c r="B18" s="87"/>
+      <c r="C18" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="89" t="s">
+      <c r="E18" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="95" t="s">
+      <c r="G18" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="96"/>
-      <c r="J18" s="74" t="s">
+      <c r="H18" s="90"/>
+      <c r="J18" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="75"/>
+      <c r="K18" s="69"/>
       <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-      <c r="E19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="E19" s="84"/>
       <c r="G19" s="33"/>
       <c r="H19" s="27" t="s">
         <v>23</v>
@@ -1949,11 +1949,11 @@
         <v>24</v>
       </c>
       <c r="C20" s="35"/>
-      <c r="D20" s="69" t="s">
+      <c r="D20" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="70"/>
-      <c r="F20" s="69" t="s">
+      <c r="E20" s="66"/>
+      <c r="F20" s="65" t="s">
         <v>18</v>
       </c>
       <c r="G20" s="36"/>
@@ -1969,9 +1969,9 @@
         <v>25</v>
       </c>
       <c r="C21" s="35"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="69"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="65"/>
       <c r="G21" s="42"/>
       <c r="H21" s="43"/>
       <c r="I21" s="38"/>
@@ -1985,9 +1985,9 @@
         <v>26</v>
       </c>
       <c r="C22" s="35"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="69"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="65"/>
       <c r="G22" s="45"/>
       <c r="H22" s="46"/>
       <c r="I22" s="38"/>
@@ -2020,84 +2020,84 @@
       <c r="A25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="73"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="101"/>
       <c r="O25" s="56"/>
     </row>
     <row r="26" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="66"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="102"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="102"/>
+      <c r="N26" s="103"/>
     </row>
     <row r="27" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
-      <c r="N27" s="66"/>
+      <c r="B27" s="102"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="102"/>
+      <c r="I27" s="102"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="102"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="102"/>
+      <c r="N27" s="103"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
+      <c r="B28" s="102"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="102"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="102"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="102"/>
+      <c r="N28" s="103"/>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="57"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="67"/>
-      <c r="M29" s="67"/>
-      <c r="N29" s="68"/>
+      <c r="B29" s="104"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="104"/>
+      <c r="N29" s="105"/>
     </row>
     <row r="30" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E30" s="58"/>
@@ -2159,36 +2159,32 @@
     <row r="65" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="71" ht="22.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="25">
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="B13:C14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B13:C14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="B25:N29"/>
+    <mergeCell ref="J18:K18"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:C19"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="G18:H18"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="B25:N25"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="B27:N27"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
